--- a/attachments/DSJ_AE_Healthcare_Operations.xlsx
+++ b/attachments/DSJ_AE_Healthcare_Operations.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D010756-B365-4AAA-B567-1E26A3CB5AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17440"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_E01B7CF6_AE3F_4C25_BC66_0A6FEA5041EC_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$57</definedName>
+    <definedName name="Z_E01B7CF6_AE3F_4C25_BC66_0A6FEA5041EC_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$58</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
   <customWorkbookViews>
@@ -20,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="316">
   <si>
     <t>First Name</t>
   </si>
@@ -972,18 +978,27 @@
   <si>
     <t>Hefei University of Technology</t>
   </si>
+  <si>
+    <t>Seyed</t>
+  </si>
+  <si>
+    <t>Emadi</t>
+  </si>
+  <si>
+    <t>Seyed_Emadi@kenan-flagler.unc.edu</t>
+  </si>
+  <si>
+    <t>University of North Carolina at Chapel Hill</t>
+  </si>
+  <si>
+    <t>Kenan-Flagler Business School</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1050,359 +1065,29 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF1155CC"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1425,254 +1110,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1692,67 +1135,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="28" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="50">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="Normal 3" xfId="28"/>
-    <cellStyle name="标题 4" xfId="29" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="30" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="31" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="32" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="33" builtinId="9"/>
-    <cellStyle name="标题" xfId="34" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="35" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="36" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="37" builtinId="40"/>
-    <cellStyle name="注释" xfId="38" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="39" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="40" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="41" builtinId="51"/>
-    <cellStyle name="超链接" xfId="42" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="43" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="44" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="46" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="48" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="49" builtinId="24"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1950,34 +1351,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z1002"/>
-  <sheetFormatPr defaultColWidth="12.6071428571429" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Z1003"/>
+  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.8839285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.2232142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="40.3839285714286" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.7232142857143" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6071428571429" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40.38671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.71875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.609375" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.1071428571429" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="31" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.1071428571429" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.1071428571429" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.109375" style="1" customWidth="1"/>
     <col min="12" max="12" width="22.5" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="12.6071428571429" style="1"/>
+    <col min="13" max="16384" width="12.609375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:12">
+    <row r="1" spans="1:12" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2015,7 +1417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:12">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -2031,7 +1433,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="15.75" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
@@ -2069,7 +1471,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:12">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
@@ -2107,7 +1509,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:12">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
@@ -2145,7 +1547,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:12">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
@@ -2183,7 +1585,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:12">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>49</v>
       </c>
@@ -2221,7 +1623,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:12">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>59</v>
       </c>
@@ -2259,7 +1661,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>64</v>
       </c>
@@ -2297,7 +1699,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:12">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>73</v>
       </c>
@@ -2335,7 +1737,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:12">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>81</v>
       </c>
@@ -2373,7 +1775,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:12">
+    <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>87</v>
       </c>
@@ -2411,7 +1813,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:12">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>95</v>
       </c>
@@ -2449,7 +1851,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:12">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>102</v>
       </c>
@@ -2487,7 +1889,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:12">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>110</v>
       </c>
@@ -2525,7 +1927,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:12">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>117</v>
       </c>
@@ -2561,7 +1963,7 @@
       </c>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:12">
+    <row r="17" spans="1:12" ht="15.75" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>123</v>
       </c>
@@ -2595,7 +1997,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:12">
+    <row r="18" spans="1:12" ht="15.75" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>130</v>
       </c>
@@ -2631,7 +2033,7 @@
       </c>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:12">
+    <row r="19" spans="1:12" ht="15.75" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>136</v>
       </c>
@@ -2667,7 +2069,7 @@
       </c>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:12">
+    <row r="20" spans="1:12" ht="15.75" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>144</v>
       </c>
@@ -2703,7 +2105,7 @@
       </c>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:12">
+    <row r="21" spans="1:12" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>151</v>
       </c>
@@ -2741,7 +2143,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:12">
+    <row r="22" spans="1:12" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>154</v>
       </c>
@@ -2775,7 +2177,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:12">
+    <row r="23" spans="1:12" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>159</v>
       </c>
@@ -2813,7 +2215,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:12">
+    <row r="24" spans="1:12" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>167</v>
       </c>
@@ -2839,15 +2241,25 @@
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A25" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -2855,75 +2267,68 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A26" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>180</v>
-      </c>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:12">
+    <row r="27" spans="1:12" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="G27" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:12">
+    <row r="28" spans="1:12" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>18</v>
@@ -2935,35 +2340,38 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:6">
+    <row r="29" spans="1:12" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A30" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A30" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>194</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>190</v>
@@ -2971,75 +2379,57 @@
       <c r="F30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="8" t="s">
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="I31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="K31" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A31" s="5" t="s">
+    <row r="32" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A32" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B32" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A32" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>18</v>
@@ -3047,83 +2437,89 @@
       <c r="G32" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="H32" s="5" t="s">
         <v>115</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A33" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="K33" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="L33" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="14"/>
-      <c r="Z32" s="14"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A33" s="4" t="s">
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+    </row>
+    <row r="34" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C34" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A34" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>18</v>
@@ -3131,191 +2527,187 @@
       <c r="G34" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="4"/>
+      <c r="I34" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+    </row>
+    <row r="35" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I35" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J35" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K35" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="L34" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A35" s="5" t="s">
+      <c r="L35" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A36" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="5" t="s">
+      <c r="F36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I36" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J36" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="K36" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="L35" s="5" t="s">
+      <c r="L36" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A36" s="4" t="s">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A37" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="4" t="s">
+      <c r="F37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H37" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I37" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="J37" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="K37" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="L36" s="4"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A37" s="4" t="s">
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A38" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="4" t="s">
+      <c r="F38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="J38" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K38" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L37" s="4" t="s">
+      <c r="L38" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A38" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="L38" s="5"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" spans="1:12">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>234</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>28</v>
+        <v>235</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>241</v>
+        <v>54</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>20</v>
@@ -3324,387 +2716,423 @@
         <v>18</v>
       </c>
       <c r="J39" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="K39" s="5" t="s">
+      <c r="K40" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="L39" s="5" t="s">
+      <c r="L40" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A40" s="5" t="s">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A41" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" s="5" t="s">
+      <c r="F41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="5" t="s">
+      <c r="I41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="5"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A41" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A42" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A43" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="F43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J43" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K43" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A43" s="4" t="s">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A44" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B44" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="4" t="s">
+      <c r="F44" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J43" s="4" t="s">
+      <c r="J44" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K44" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="L43" s="4" t="s">
+      <c r="L44" s="4" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A44" s="9" t="s">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A45" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B45" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C45" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D45" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E45" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="9" t="s">
+      <c r="F45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H45" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J45" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="K44" s="9" t="s">
+      <c r="K45" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="L44" s="9" t="s">
+      <c r="L45" s="9" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A45" s="10" t="s">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A46" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B46" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C46" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D46" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E46" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="F46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H46" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="I46" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="J46" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="K45" s="9" t="s">
+      <c r="K46" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="L46" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A46" s="9" t="s">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A47" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B47" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C47" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D47" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E47" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G46" s="9" t="s">
+      <c r="F47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="I47" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="J46" s="9" t="s">
+      <c r="J47" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+    </row>
+    <row r="48" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A48" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="F48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="K48" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="14" spans="1:12">
-      <c r="A48" s="11" t="s">
+    <row r="49" spans="1:12" customFormat="1" ht="14.4">
+      <c r="A49" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B49" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="5" t="s">
+      <c r="F49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+    </row>
+    <row r="50" spans="1:12" ht="14.4">
+      <c r="A50" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5" t="s">
+      <c r="D50" s="5"/>
+      <c r="E50" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:5">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="13"/>
-      <c r="E50" s="12"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+      <c r="F50" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="13"/>
+      <c r="E51" s="12"/>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="53" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="54" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="55" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="56" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="57" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="58" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="16"/>
+    </row>
+    <row r="59" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="60" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="61" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -4643,23 +4071,23 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{E01B7CF6-AE3F-4C25-BC66-0A6FEA5041EC}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <headerFooter/>
-      <autoFilter ref="A1:L60"/>
+      <autoFilter ref="A1:L60" xr:uid="{69B2F1DE-E5C3-49DB-8814-3074757BEFE2}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="1">
-    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="K58:L58"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C24" r:id="rId1" display="C.Vasilakis@bath.ac.uk"/>
+    <hyperlink ref="C24" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C25" r:id="rId2" xr:uid="{EA6ACB44-1BF9-4A19-8E72-6AA81C6D35AF}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="1" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <headerFooter/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>